--- a/data/tasques/02.20/ADG32/entregues/5796/02.20-5796-03_FACTURES_COMPRA.xlsx
+++ b/data/tasques/02.20/ADG32/entregues/5796/02.20-5796-03_FACTURES_COMPRA.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="289">
   <si>
     <t>Número</t>
   </si>
@@ -46,213 +46,636 @@
     <t>Estado en pago</t>
   </si>
   <si>
+    <t>FC/2026/0054</t>
+  </si>
+  <si>
+    <t>IBERBANK</t>
+  </si>
+  <si>
+    <t>27594362</t>
+  </si>
+  <si>
+    <t>Pagada</t>
+  </si>
+  <si>
+    <t>FC/2026/0039</t>
+  </si>
+  <si>
+    <t>ADG32 6702 NFORNES SL</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00023</t>
+  </si>
+  <si>
+    <t>FC/2026/0053</t>
+  </si>
+  <si>
+    <t>27554533</t>
+  </si>
+  <si>
+    <t>FC/2026/0052</t>
+  </si>
+  <si>
+    <t>27554513</t>
+  </si>
+  <si>
+    <t>FC/2026/0027</t>
+  </si>
+  <si>
+    <t>ADG32 6713 BCARBONELL SL</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00021</t>
+  </si>
+  <si>
+    <t>FC/2026/0022</t>
+  </si>
+  <si>
+    <t>ALUBIX SL</t>
+  </si>
+  <si>
+    <t>2026/00060</t>
+  </si>
+  <si>
+    <t>C-C/00038</t>
+  </si>
+  <si>
+    <t>FC/2026/0021</t>
+  </si>
+  <si>
+    <t>ROCALLA SA</t>
+  </si>
+  <si>
+    <t>2026/00056</t>
+  </si>
+  <si>
+    <t>C-C/00037</t>
+  </si>
+  <si>
+    <t>FC/2026/0051</t>
+  </si>
+  <si>
+    <t>27464860</t>
+  </si>
+  <si>
+    <t>FC/2026/0050</t>
+  </si>
+  <si>
+    <t>27464845</t>
+  </si>
+  <si>
+    <t>FC/2026/0043</t>
+  </si>
+  <si>
+    <t>ADG32 6844 TTRAMULLAS SL</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00006</t>
+  </si>
+  <si>
+    <t>FC/2026/0040</t>
+  </si>
+  <si>
+    <t>ADG32 6792 PCAPO SL</t>
+  </si>
+  <si>
+    <t>FV-1/2026/00015</t>
+  </si>
+  <si>
+    <t>Publicado</t>
+  </si>
+  <si>
+    <t>FC/2026/0025</t>
+  </si>
+  <si>
+    <t>ADG32 6707 MOUAZINE SL</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00022</t>
+  </si>
+  <si>
+    <t>FC/2026/0046</t>
+  </si>
+  <si>
+    <t>ADG32 6467 WCHANTAH SL</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00024</t>
+  </si>
+  <si>
+    <t>FC/2026/0037</t>
+  </si>
+  <si>
+    <t>ADG32 6706 NSUIYHI SL</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00014</t>
+  </si>
+  <si>
+    <t>FC/2026/0031</t>
+  </si>
+  <si>
+    <t>ADG32 6777 JGARCIA SL</t>
+  </si>
+  <si>
+    <t>FC/2026/0045</t>
+  </si>
+  <si>
+    <t>ADG32 6356 WAANANOU SL</t>
+  </si>
+  <si>
+    <t>FC/2026/0038</t>
+  </si>
+  <si>
+    <t>ADG32 6427 NANANOU SL</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00016</t>
+  </si>
+  <si>
+    <t>FC/2026/0044</t>
+  </si>
+  <si>
+    <t>ADG32 6369 VMASTRANGELO SL</t>
+  </si>
+  <si>
+    <t>FC/2026/0036</t>
+  </si>
+  <si>
+    <t>ADG32 6265 SMORENO SL</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00012</t>
+  </si>
+  <si>
+    <t>FC/2026/0034</t>
+  </si>
+  <si>
+    <t>ADG32 6368 LPIZA SL</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00004</t>
+  </si>
+  <si>
+    <t>FC/2026/0033</t>
+  </si>
+  <si>
+    <t>ADG32 6734 LABOLAFIO SL</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00007</t>
+  </si>
+  <si>
+    <t>FC/2026/0032</t>
+  </si>
+  <si>
+    <t>ADG32 6366 JMORAGUES SL</t>
+  </si>
+  <si>
     <t>FC/2026/0028</t>
   </si>
   <si>
-    <t>ROCALLA SA</t>
-  </si>
-  <si>
-    <t>2026/00063</t>
+    <t>ADG32 6478 CBAUZA SL</t>
+  </si>
+  <si>
+    <t>Factura FV-2/2026/00015</t>
+  </si>
+  <si>
+    <t>FC/2026/0049</t>
+  </si>
+  <si>
+    <t>27390600</t>
+  </si>
+  <si>
+    <t>FC/2026/0035</t>
+  </si>
+  <si>
+    <t>ADG32 6320 MNAVARRO SL</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00008</t>
+  </si>
+  <si>
+    <t>FC/2026/0030</t>
+  </si>
+  <si>
+    <t>ADG32 6431 GZOUGGAGHI SL</t>
+  </si>
+  <si>
+    <t>Factura FV-2/2026/00014</t>
+  </si>
+  <si>
+    <t>FC/2026/0029</t>
+  </si>
+  <si>
+    <t>ADG32 6746 ELLADO SL</t>
+  </si>
+  <si>
+    <t>Factura FV-2/2026/00010</t>
+  </si>
+  <si>
+    <t>FC/2026/0026</t>
+  </si>
+  <si>
+    <t>ADG32 6428 ABOUBAL SL</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00015</t>
+  </si>
+  <si>
+    <t>FC/2026/0013</t>
+  </si>
+  <si>
+    <t>2026/00055</t>
+  </si>
+  <si>
+    <t>C-C/00036</t>
+  </si>
+  <si>
+    <t>FC/2026/0012</t>
+  </si>
+  <si>
+    <t>C-C/00035</t>
+  </si>
+  <si>
+    <t>FC/2026/0048</t>
+  </si>
+  <si>
+    <t>ELECTROQT SA</t>
+  </si>
+  <si>
+    <t>1072688</t>
+  </si>
+  <si>
+    <t>FC/2026/0041</t>
+  </si>
+  <si>
+    <t>ADG32 6352 SAANANOU SL</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00013</t>
+  </si>
+  <si>
+    <t>FC/2026/0047</t>
+  </si>
+  <si>
+    <t>TELEKOMM SA</t>
+  </si>
+  <si>
+    <t>1071183</t>
+  </si>
+  <si>
+    <t>FC/2026/0016</t>
+  </si>
+  <si>
+    <t>OFFISPACE SA</t>
+  </si>
+  <si>
+    <t>1067870</t>
+  </si>
+  <si>
+    <t>FC/2026/0042</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00003</t>
+  </si>
+  <si>
+    <t>FC/2026/0024</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00002</t>
+  </si>
+  <si>
+    <t>FC/2026/0011</t>
+  </si>
+  <si>
+    <t>2026/00051</t>
   </si>
   <si>
     <t>C-C/00034</t>
   </si>
   <si>
-    <t>Pagada</t>
-  </si>
-  <si>
-    <t>FC/2026/0027</t>
-  </si>
-  <si>
-    <t>ALUBIX SL</t>
-  </si>
-  <si>
-    <t>2026/00051</t>
+    <t>FC/2026/0010</t>
+  </si>
+  <si>
+    <t>2026/00054</t>
   </si>
   <si>
     <t>C-C/00033</t>
   </si>
   <si>
-    <t>FC/2026/0026</t>
-  </si>
-  <si>
-    <t>2026/00059</t>
+    <t>FC/2026/0009</t>
+  </si>
+  <si>
+    <t>2026/00046</t>
   </si>
   <si>
     <t>C-C/00032</t>
   </si>
   <si>
-    <t>FC/2026/0025</t>
-  </si>
-  <si>
-    <t>2026/00047</t>
+    <t>FC/2026/0020</t>
+  </si>
+  <si>
+    <t>27283733</t>
+  </si>
+  <si>
+    <t>FC/2026/0023</t>
+  </si>
+  <si>
+    <t>FV-2/2026/00001</t>
+  </si>
+  <si>
+    <t>FC/2026/0008</t>
+  </si>
+  <si>
+    <t>2026/00045</t>
+  </si>
+  <si>
+    <t>C-C/00030</t>
+  </si>
+  <si>
+    <t>FC/2026/0007</t>
+  </si>
+  <si>
+    <t>2026/00053</t>
   </si>
   <si>
     <t>C-C/00031</t>
   </si>
   <si>
+    <t>FC/2026/0019</t>
+  </si>
+  <si>
+    <t>27200596</t>
+  </si>
+  <si>
+    <t>FC/2026/0018</t>
+  </si>
+  <si>
+    <t>27200576</t>
+  </si>
+  <si>
+    <t>FC/2026/0006</t>
+  </si>
+  <si>
+    <t>2026/00049</t>
+  </si>
+  <si>
+    <t>C-C/00029</t>
+  </si>
+  <si>
+    <t>FC/2026/0005</t>
+  </si>
+  <si>
+    <t>2026/00041</t>
+  </si>
+  <si>
+    <t>C-C/00028</t>
+  </si>
+  <si>
+    <t>FC/2026/0017</t>
+  </si>
+  <si>
+    <t>27143469</t>
+  </si>
+  <si>
+    <t>FC/2026/0004</t>
+  </si>
+  <si>
+    <t>2026/00039</t>
+  </si>
+  <si>
+    <t>C-C/00027</t>
+  </si>
+  <si>
+    <t>FC/2026/0003</t>
+  </si>
+  <si>
+    <t>C-C/00026</t>
+  </si>
+  <si>
+    <t>FC/2026/0002</t>
+  </si>
+  <si>
+    <t>2026/00044</t>
+  </si>
+  <si>
+    <t>C-C/00025</t>
+  </si>
+  <si>
+    <t>FC/2026/0001</t>
+  </si>
+  <si>
+    <t>2026/00038</t>
+  </si>
+  <si>
+    <t>C-C/00024</t>
+  </si>
+  <si>
     <t>FC/2026/0015</t>
   </si>
   <si>
-    <t>2026/00055</t>
-  </si>
-  <si>
-    <t>C-C/00030</t>
+    <t>1060446</t>
   </si>
   <si>
     <t>FC/2026/0014</t>
   </si>
   <si>
-    <t>2026/00044</t>
-  </si>
-  <si>
-    <t>C-C/00029</t>
-  </si>
-  <si>
-    <t>FC/2026/0010</t>
-  </si>
-  <si>
-    <t>2026/00050</t>
-  </si>
-  <si>
-    <t>C-C/00028</t>
-  </si>
-  <si>
-    <t>FC/2026/0009</t>
-  </si>
-  <si>
-    <t>2026/00043</t>
-  </si>
-  <si>
-    <t>C-C/00027</t>
-  </si>
-  <si>
-    <t>FC/2026/0006</t>
-  </si>
-  <si>
-    <t>2026/00046</t>
-  </si>
-  <si>
-    <t>C-C/00026</t>
-  </si>
-  <si>
-    <t>FC/2026/0005</t>
-  </si>
-  <si>
-    <t>2026/00040</t>
-  </si>
-  <si>
-    <t>C-C/00025</t>
-  </si>
-  <si>
-    <t>FC/2026/0004</t>
-  </si>
-  <si>
-    <t>2026/00042</t>
-  </si>
-  <si>
-    <t>C-C/00024</t>
-  </si>
-  <si>
-    <t>FC/2026/0003</t>
-  </si>
-  <si>
-    <t>2026/00037</t>
+    <t>105662</t>
+  </si>
+  <si>
+    <t>FC/2025/0057</t>
+  </si>
+  <si>
+    <t>1055590</t>
+  </si>
+  <si>
+    <t>FC/2025/0048</t>
+  </si>
+  <si>
+    <t>2025/00034</t>
+  </si>
+  <si>
+    <t>C-C/00022</t>
+  </si>
+  <si>
+    <t>FC/2025/0047</t>
+  </si>
+  <si>
+    <t>2025/00041</t>
   </si>
   <si>
     <t>C-C/00023</t>
   </si>
   <si>
+    <t>FC/2025/0056</t>
+  </si>
+  <si>
+    <t>26911082</t>
+  </si>
+  <si>
+    <t>FC/2025/0055</t>
+  </si>
+  <si>
+    <t>26911100</t>
+  </si>
+  <si>
+    <t>FC/2025/0054</t>
+  </si>
+  <si>
+    <t>26835262</t>
+  </si>
+  <si>
     <t>FC/2025/0053</t>
   </si>
   <si>
-    <t>2025/00039</t>
-  </si>
-  <si>
-    <t>C-C/00022</t>
+    <t>26835243</t>
+  </si>
+  <si>
+    <t>FC/2025/0046</t>
+  </si>
+  <si>
+    <t>2025/00037</t>
+  </si>
+  <si>
+    <t>C-C/00021</t>
+  </si>
+  <si>
+    <t>FC/2025/0045</t>
+  </si>
+  <si>
+    <t>2025/00032</t>
+  </si>
+  <si>
+    <t>C-C/00020</t>
   </si>
   <si>
     <t>FC/2025/0052</t>
   </si>
   <si>
-    <t>2025/00036</t>
-  </si>
-  <si>
-    <t>C-C/00021</t>
+    <t>26755613</t>
+  </si>
+  <si>
+    <t>FC/2025/0044</t>
+  </si>
+  <si>
+    <t>2025/00028</t>
+  </si>
+  <si>
+    <t>C-C/00019</t>
+  </si>
+  <si>
+    <t>FC/2025/0043</t>
+  </si>
+  <si>
+    <t>C-C/00018</t>
+  </si>
+  <si>
+    <t>FC/2025/0042</t>
+  </si>
+  <si>
+    <t>C-C/00017</t>
+  </si>
+  <si>
+    <t>Cancelado</t>
+  </si>
+  <si>
+    <t>FC/2025/0039</t>
+  </si>
+  <si>
+    <t>26559313</t>
   </si>
   <si>
     <t>FC/2025/0051</t>
   </si>
   <si>
-    <t>C-C/00020</t>
+    <t>26688404</t>
   </si>
   <si>
     <t>FC/2025/0050</t>
   </si>
   <si>
-    <t>2025/00031</t>
-  </si>
-  <si>
-    <t>C-C/00019</t>
-  </si>
-  <si>
-    <t>FC/2025/0047</t>
-  </si>
-  <si>
-    <t>2025/00035</t>
-  </si>
-  <si>
-    <t>C-C/00018</t>
-  </si>
-  <si>
-    <t>FC/2025/0046</t>
-  </si>
-  <si>
-    <t>2025/00028</t>
-  </si>
-  <si>
-    <t>C-C/00017</t>
+    <t>26688384</t>
+  </si>
+  <si>
+    <t>FC/2025/0049</t>
+  </si>
+  <si>
+    <t>26688366</t>
+  </si>
+  <si>
+    <t>FC/2025/0038</t>
+  </si>
+  <si>
+    <t>54940</t>
+  </si>
+  <si>
+    <t>FC/2025/0037</t>
+  </si>
+  <si>
+    <t>1048728</t>
+  </si>
+  <si>
+    <t>FC/2025/0035</t>
+  </si>
+  <si>
+    <t>2025/00024</t>
+  </si>
+  <si>
+    <t>C-C/00016</t>
+  </si>
+  <si>
+    <t>FC/2025/0034</t>
+  </si>
+  <si>
+    <t>2025/00027</t>
+  </si>
+  <si>
+    <t>C-C/00015</t>
+  </si>
+  <si>
+    <t>FC/2025/0036</t>
+  </si>
+  <si>
+    <t>1045911</t>
   </si>
   <si>
     <t>FC/2025/0041</t>
   </si>
   <si>
-    <t>2025/00030</t>
-  </si>
-  <si>
-    <t>C-C/00016</t>
+    <t>26559352</t>
   </si>
   <si>
     <t>FC/2025/0040</t>
   </si>
   <si>
-    <t>2025/00025</t>
-  </si>
-  <si>
-    <t>C-C/00015</t>
+    <t>26559333</t>
   </si>
   <si>
     <t>FC/2025/0033</t>
   </si>
   <si>
-    <t>2025/00029</t>
+    <t>2025/00022</t>
+  </si>
+  <si>
+    <t>C-C/00013</t>
+  </si>
+  <si>
+    <t>FC/2025/0032</t>
+  </si>
+  <si>
+    <t>2025/00021</t>
   </si>
   <si>
     <t>C-C/00014</t>
   </si>
   <si>
-    <t>FC/2025/0032</t>
-  </si>
-  <si>
-    <t>2025/00020</t>
-  </si>
-  <si>
-    <t>C-C/00013</t>
-  </si>
-  <si>
     <t>FC/2025/0028</t>
   </si>
   <si>
+    <t>2025/00017</t>
+  </si>
+  <si>
     <t>C-C/00012</t>
   </si>
   <si>
@@ -265,91 +688,199 @@
     <t>C-C/00011</t>
   </si>
   <si>
+    <t>FC/2025/0031</t>
+  </si>
+  <si>
+    <t>26469042</t>
+  </si>
+  <si>
+    <t>FC/2025/0030</t>
+  </si>
+  <si>
+    <t>26469022</t>
+  </si>
+  <si>
+    <t>FC/2025/0029</t>
+  </si>
+  <si>
+    <t>26469002</t>
+  </si>
+  <si>
     <t>FC/2025/0010</t>
   </si>
   <si>
+    <t>C-C/00009</t>
+  </si>
+  <si>
+    <t>FC/2025/0009</t>
+  </si>
+  <si>
+    <t>2025/00013</t>
+  </si>
+  <si>
     <t>C-C/00010</t>
   </si>
   <si>
-    <t>FC/2025/0009</t>
-  </si>
-  <si>
-    <t>2025/00014</t>
-  </si>
-  <si>
-    <t>C-C/00009</t>
+    <t>FC/2025/0026</t>
+  </si>
+  <si>
+    <t>26386998</t>
+  </si>
+  <si>
+    <t>FC/2025/0025</t>
+  </si>
+  <si>
+    <t>26386979</t>
+  </si>
+  <si>
+    <t>FC/2025/0024</t>
+  </si>
+  <si>
+    <t>26386960</t>
+  </si>
+  <si>
+    <t>FC/2025/0023</t>
+  </si>
+  <si>
+    <t>26322944</t>
+  </si>
+  <si>
+    <t>FC/2025/0022</t>
+  </si>
+  <si>
+    <t>26322924</t>
+  </si>
+  <si>
+    <t>FC/2025/0021</t>
+  </si>
+  <si>
+    <t>26322905</t>
+  </si>
+  <si>
+    <t>FC/2025/0020</t>
+  </si>
+  <si>
+    <t>26322887</t>
+  </si>
+  <si>
+    <t>FC/2025/0019</t>
+  </si>
+  <si>
+    <t>26322869</t>
+  </si>
+  <si>
+    <t>FC/2025/0018</t>
+  </si>
+  <si>
+    <t>26322851</t>
   </si>
   <si>
     <t>FC/2025/0008</t>
   </si>
   <si>
-    <t>2025/00015</t>
-  </si>
-  <si>
     <t>C-C/00008</t>
   </si>
   <si>
     <t>FC/2025/0007</t>
   </si>
   <si>
-    <t>2025/00011</t>
+    <t>2025/00008</t>
   </si>
   <si>
     <t>C-C/00007</t>
   </si>
   <si>
+    <t>FC/2025/0014</t>
+  </si>
+  <si>
+    <t>1038651</t>
+  </si>
+  <si>
+    <t>FC/2025/0012</t>
+  </si>
+  <si>
+    <t>1037562</t>
+  </si>
+  <si>
+    <t>FC/2025/0016</t>
+  </si>
+  <si>
+    <t>1035405</t>
+  </si>
+  <si>
     <t>FC/2025/0006</t>
   </si>
   <si>
-    <t>2025/00013</t>
+    <t>2025/00006</t>
+  </si>
+  <si>
+    <t>C-C/00005</t>
+  </si>
+  <si>
+    <t>FC/2025/0005</t>
+  </si>
+  <si>
+    <t>2025/00010</t>
   </si>
   <si>
     <t>C-C/00006</t>
   </si>
   <si>
-    <t>FC/2025/0005</t>
-  </si>
-  <si>
-    <t>2025/00006</t>
-  </si>
-  <si>
-    <t>C-C/00005</t>
-  </si>
-  <si>
     <t>FC/2025/0004</t>
   </si>
   <si>
-    <t>2025/00009</t>
+    <t>2025/00005</t>
+  </si>
+  <si>
+    <t>C-C/00003</t>
+  </si>
+  <si>
+    <t>FC/2025/0003</t>
   </si>
   <si>
     <t>C-C/00004</t>
   </si>
   <si>
-    <t>FC/2025/0003</t>
-  </si>
-  <si>
-    <t>2025/00003</t>
-  </si>
-  <si>
-    <t>C-C/00003</t>
+    <t>FC/2025/0017</t>
+  </si>
+  <si>
+    <t>26189451</t>
   </si>
   <si>
     <t>FC/2025/0002</t>
   </si>
   <si>
-    <t>2025/00005</t>
+    <t>2025/00001</t>
+  </si>
+  <si>
+    <t>C-C/00002</t>
+  </si>
+  <si>
+    <t>FC/2025/0001</t>
+  </si>
+  <si>
+    <t>2025/00002</t>
   </si>
   <si>
     <t>C-C/00001</t>
   </si>
   <si>
-    <t>FC/2025/0001</t>
-  </si>
-  <si>
-    <t>2025/00002</t>
-  </si>
-  <si>
-    <t>C-C/00002</t>
+    <t>FC/2025/0013</t>
+  </si>
+  <si>
+    <t>1026829</t>
+  </si>
+  <si>
+    <t>FC/2025/0011</t>
+  </si>
+  <si>
+    <t>1025959</t>
+  </si>
+  <si>
+    <t>FC/2025/0015</t>
+  </si>
+  <si>
+    <t>1024557</t>
   </si>
 </sst>
 </file>
@@ -703,7 +1234,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="10" width="30.7109375" customWidth="1"/>
@@ -752,1081 +1283,3399 @@
         <v>12</v>
       </c>
       <c r="D2" s="3">
-        <v>46064</v>
+        <v>46074</v>
       </c>
       <c r="E2" s="3">
-        <v>46071</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>13</v>
-      </c>
+        <v>46074</v>
+      </c>
+      <c r="F2" s="2"/>
       <c r="G2" s="4">
-        <v>-3699</v>
+        <v>-1</v>
       </c>
       <c r="H2" s="4">
-        <v>-776.79</v>
+        <v>-0.21</v>
       </c>
       <c r="I2" s="4">
-        <v>-4475.79</v>
+        <v>-1.21</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="D3" s="3">
-        <v>46064</v>
+        <v>46062</v>
       </c>
       <c r="E3" s="3">
-        <v>46071</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>18</v>
-      </c>
+        <v>46062</v>
+      </c>
+      <c r="F3" s="2"/>
       <c r="G3" s="4">
-        <v>-3122</v>
+        <v>-414</v>
       </c>
       <c r="H3" s="4">
-        <v>-655.62</v>
+        <v>-86.94</v>
       </c>
       <c r="I3" s="4">
-        <v>-3777.62</v>
+        <v>-500.94</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D4" s="3">
-        <v>46057</v>
+        <v>46071</v>
       </c>
       <c r="E4" s="3">
-        <v>46064</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>21</v>
-      </c>
+        <v>46071</v>
+      </c>
+      <c r="F4" s="2"/>
       <c r="G4" s="4">
-        <v>-6738</v>
+        <v>-1</v>
       </c>
       <c r="H4" s="4">
-        <v>-1414.98</v>
+        <v>-0.21</v>
       </c>
       <c r="I4" s="4">
-        <v>-8152.98</v>
+        <v>-1.21</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D5" s="3">
-        <v>46057</v>
+        <v>46071</v>
       </c>
       <c r="E5" s="3">
-        <v>46064</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>24</v>
-      </c>
+        <v>46071</v>
+      </c>
+      <c r="F5" s="2"/>
       <c r="G5" s="4">
-        <v>-6158</v>
+        <v>-1</v>
       </c>
       <c r="H5" s="4">
-        <v>-1293.18</v>
+        <v>-0.21</v>
       </c>
       <c r="I5" s="4">
-        <v>-7451.18</v>
+        <v>-1.21</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D6" s="3">
-        <v>46050</v>
+        <v>46065</v>
       </c>
       <c r="E6" s="3">
-        <v>46057</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>27</v>
-      </c>
+        <v>46065</v>
+      </c>
+      <c r="F6" s="2"/>
       <c r="G6" s="4">
-        <v>-3759</v>
+        <v>-398.25</v>
       </c>
       <c r="H6" s="4">
-        <v>-789.39</v>
+        <v>-83.63</v>
       </c>
       <c r="I6" s="4">
-        <v>-4548.39</v>
+        <v>-481.88</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D7" s="3">
-        <v>46050</v>
+        <v>46064</v>
       </c>
       <c r="E7" s="3">
-        <v>46057</v>
+        <v>46071</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G7" s="4">
-        <v>-3086</v>
+        <v>-3618</v>
       </c>
       <c r="H7" s="4">
-        <v>-648.0599999999999</v>
+        <v>-759.78</v>
       </c>
       <c r="I7" s="4">
-        <v>-3734.06</v>
+        <v>-4377.78</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="3">
+        <v>46064</v>
+      </c>
+      <c r="E8" s="3">
+        <v>46071</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="3">
-        <v>46043</v>
-      </c>
-      <c r="E8" s="3">
-        <v>46050</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="G8" s="4">
-        <v>-3801</v>
+        <v>-3982</v>
       </c>
       <c r="H8" s="4">
-        <v>-798.21</v>
+        <v>-836.22</v>
       </c>
       <c r="I8" s="4">
-        <v>-4599.21</v>
+        <v>-4818.22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D9" s="3">
-        <v>46043</v>
+        <v>46064</v>
       </c>
       <c r="E9" s="3">
-        <v>46050</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>36</v>
-      </c>
+        <v>46064</v>
+      </c>
+      <c r="F9" s="2"/>
       <c r="G9" s="4">
-        <v>-3198</v>
+        <v>-1</v>
       </c>
       <c r="H9" s="4">
-        <v>-671.58</v>
+        <v>-0.21</v>
       </c>
       <c r="I9" s="4">
-        <v>-3869.58</v>
+        <v>-1.21</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D10" s="3">
-        <v>46036</v>
+        <v>46064</v>
       </c>
       <c r="E10" s="3">
-        <v>46043</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>39</v>
-      </c>
+        <v>46064</v>
+      </c>
+      <c r="F10" s="2"/>
       <c r="G10" s="4">
-        <v>-3393</v>
+        <v>-1</v>
       </c>
       <c r="H10" s="4">
-        <v>-712.53</v>
+        <v>-0.21</v>
       </c>
       <c r="I10" s="4">
-        <v>-4105.53</v>
+        <v>-1.21</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D11" s="3">
-        <v>46036</v>
+        <v>46064</v>
       </c>
       <c r="E11" s="3">
-        <v>46043</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>42</v>
-      </c>
+        <v>46064</v>
+      </c>
+      <c r="F11" s="2"/>
       <c r="G11" s="4">
-        <v>-3132</v>
+        <v>-402</v>
       </c>
       <c r="H11" s="4">
-        <v>-657.72</v>
+        <v>-84.42</v>
       </c>
       <c r="I11" s="4">
-        <v>-3789.72</v>
+        <v>-486.42</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D12" s="3">
-        <v>46030</v>
+        <v>46064</v>
       </c>
       <c r="E12" s="3">
-        <v>46037</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>45</v>
-      </c>
+        <v>46064</v>
+      </c>
+      <c r="F12" s="2"/>
       <c r="G12" s="4">
-        <v>-3525</v>
+        <v>-418.5</v>
       </c>
       <c r="H12" s="4">
-        <v>-740.25</v>
+        <v>-87.89</v>
       </c>
       <c r="I12" s="4">
-        <v>-4265.25</v>
+        <v>-506.39</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D13" s="3">
-        <v>46030</v>
+        <v>46064</v>
       </c>
       <c r="E13" s="3">
-        <v>46037</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>48</v>
-      </c>
+        <v>46064</v>
+      </c>
+      <c r="F13" s="2"/>
       <c r="G13" s="4">
-        <v>-3132</v>
+        <v>-396</v>
       </c>
       <c r="H13" s="4">
-        <v>-657.72</v>
+        <v>-83.16</v>
       </c>
       <c r="I13" s="4">
-        <v>-3789.72</v>
+        <v>-479.16</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D14" s="3">
-        <v>46015</v>
+        <v>46063</v>
       </c>
       <c r="E14" s="3">
-        <v>46022</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>51</v>
-      </c>
+        <v>46063</v>
+      </c>
+      <c r="F14" s="2"/>
       <c r="G14" s="4">
-        <v>-135</v>
+        <v>-400.5</v>
       </c>
       <c r="H14" s="4">
-        <v>-28.35</v>
+        <v>-84.11</v>
       </c>
       <c r="I14" s="4">
-        <v>-163.35</v>
+        <v>-484.61</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D15" s="3">
-        <v>46015</v>
+        <v>46063</v>
       </c>
       <c r="E15" s="3">
-        <v>46022</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>54</v>
-      </c>
+        <v>46063</v>
+      </c>
+      <c r="F15" s="2"/>
       <c r="G15" s="4">
-        <v>-134</v>
+        <v>-396</v>
       </c>
       <c r="H15" s="4">
-        <v>-28.14</v>
+        <v>-83.16</v>
       </c>
       <c r="I15" s="4">
-        <v>-162.14</v>
+        <v>-479.16</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="D16" s="3">
-        <v>46009</v>
+        <v>46063</v>
       </c>
       <c r="E16" s="3">
-        <v>46016</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>56</v>
-      </c>
+        <v>46063</v>
+      </c>
+      <c r="F16" s="2"/>
       <c r="G16" s="4">
-        <v>-3114</v>
+        <v>-396</v>
       </c>
       <c r="H16" s="4">
-        <v>-653.9400000000001</v>
+        <v>-83.16</v>
       </c>
       <c r="I16" s="4">
-        <v>-3767.94</v>
+        <v>-479.16</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="D17" s="3">
-        <v>46009</v>
+        <v>46060</v>
       </c>
       <c r="E17" s="3">
-        <v>46016</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>59</v>
-      </c>
+        <v>46060</v>
+      </c>
+      <c r="F17" s="2"/>
       <c r="G17" s="4">
-        <v>-2788</v>
+        <v>-391.5</v>
       </c>
       <c r="H17" s="4">
-        <v>-585.48</v>
+        <v>-82.22</v>
       </c>
       <c r="I17" s="4">
-        <v>-3373.48</v>
+        <v>-473.72</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D18" s="3">
-        <v>46001</v>
+        <v>46060</v>
       </c>
       <c r="E18" s="3">
-        <v>46008</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>62</v>
-      </c>
+        <v>46060</v>
+      </c>
+      <c r="F18" s="2"/>
       <c r="G18" s="4">
-        <v>-3462</v>
+        <v>-408</v>
       </c>
       <c r="H18" s="4">
-        <v>-727.02</v>
+        <v>-85.68000000000001</v>
       </c>
       <c r="I18" s="4">
-        <v>-4189.02</v>
+        <v>-493.68</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="D19" s="3">
-        <v>46001</v>
+        <v>46059</v>
       </c>
       <c r="E19" s="3">
-        <v>46008</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>65</v>
-      </c>
+        <v>46059</v>
+      </c>
+      <c r="F19" s="2"/>
       <c r="G19" s="4">
-        <v>-2886</v>
+        <v>-393</v>
       </c>
       <c r="H19" s="4">
-        <v>-606.0599999999999</v>
+        <v>-82.53</v>
       </c>
       <c r="I19" s="4">
-        <v>-3492.06</v>
+        <v>-475.53</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D20" s="3">
-        <v>45994</v>
+        <v>46059</v>
       </c>
       <c r="E20" s="3">
-        <v>46001</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>68</v>
-      </c>
+        <v>46059</v>
+      </c>
+      <c r="F20" s="2"/>
       <c r="G20" s="4">
-        <v>-3591</v>
+        <v>-394.5</v>
       </c>
       <c r="H20" s="4">
-        <v>-754.11</v>
+        <v>-82.84999999999999</v>
       </c>
       <c r="I20" s="4">
-        <v>-4345.11</v>
+        <v>-477.35</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D21" s="3">
-        <v>45994</v>
+        <v>46059</v>
       </c>
       <c r="E21" s="3">
-        <v>46001</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>71</v>
-      </c>
+        <v>46059</v>
+      </c>
+      <c r="F21" s="2"/>
       <c r="G21" s="4">
-        <v>-2956</v>
+        <v>-414</v>
       </c>
       <c r="H21" s="4">
-        <v>-620.76</v>
+        <v>-86.94</v>
       </c>
       <c r="I21" s="4">
-        <v>-3576.76</v>
+        <v>-500.94</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D22" s="3">
-        <v>45987</v>
+        <v>46059</v>
       </c>
       <c r="E22" s="3">
-        <v>45994</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>74</v>
-      </c>
+        <v>46059</v>
+      </c>
+      <c r="F22" s="2"/>
       <c r="G22" s="4">
-        <v>-3525</v>
+        <v>-415.5</v>
       </c>
       <c r="H22" s="4">
-        <v>-740.25</v>
+        <v>-87.26000000000001</v>
       </c>
       <c r="I22" s="4">
-        <v>-4265.25</v>
+        <v>-502.76</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="D23" s="3">
-        <v>45987</v>
+        <v>46059</v>
       </c>
       <c r="E23" s="3">
-        <v>45994</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>77</v>
-      </c>
+        <v>46059</v>
+      </c>
+      <c r="F23" s="2"/>
       <c r="G23" s="4">
-        <v>-3190</v>
+        <v>-403.5</v>
       </c>
       <c r="H23" s="4">
-        <v>-669.9</v>
+        <v>-84.73999999999999</v>
       </c>
       <c r="I23" s="4">
-        <v>-3859.9</v>
+        <v>-488.24</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D24" s="3">
-        <v>45980</v>
+        <v>46059</v>
       </c>
       <c r="E24" s="3">
-        <v>45987</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>79</v>
-      </c>
+        <v>46059</v>
+      </c>
+      <c r="F24" s="2"/>
       <c r="G24" s="4">
-        <v>-3114</v>
+        <v>-399</v>
       </c>
       <c r="H24" s="4">
-        <v>-653.9400000000001</v>
+        <v>-83.79000000000001</v>
       </c>
       <c r="I24" s="4">
-        <v>-3767.94</v>
+        <v>-482.79</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="D25" s="3">
-        <v>45980</v>
+        <v>46058</v>
       </c>
       <c r="E25" s="3">
-        <v>45987</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>82</v>
-      </c>
+        <v>46058</v>
+      </c>
+      <c r="F25" s="2"/>
       <c r="G25" s="4">
-        <v>-2736</v>
+        <v>-1</v>
       </c>
       <c r="H25" s="4">
-        <v>-574.5599999999999</v>
+        <v>-0.21</v>
       </c>
       <c r="I25" s="4">
-        <v>-3310.56</v>
+        <v>-1.21</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>11</v>
+        <v>78</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D26" s="3">
-        <v>45973</v>
+        <v>46058</v>
       </c>
       <c r="E26" s="3">
-        <v>45980</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>84</v>
-      </c>
+        <v>46058</v>
+      </c>
+      <c r="F26" s="2"/>
       <c r="G26" s="4">
-        <v>-3945</v>
+        <v>-402</v>
       </c>
       <c r="H26" s="4">
-        <v>-828.45</v>
+        <v>-84.42</v>
       </c>
       <c r="I26" s="4">
-        <v>-4773.45</v>
+        <v>-486.42</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D27" s="3">
-        <v>45973</v>
+        <v>46058</v>
       </c>
       <c r="E27" s="3">
-        <v>45980</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>87</v>
-      </c>
+        <v>46058</v>
+      </c>
+      <c r="F27" s="2"/>
       <c r="G27" s="4">
-        <v>-2946</v>
+        <v>-423</v>
       </c>
       <c r="H27" s="4">
-        <v>-618.66</v>
+        <v>-88.83</v>
       </c>
       <c r="I27" s="4">
-        <v>-3564.66</v>
+        <v>-511.83</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D28" s="3">
-        <v>45966</v>
+        <v>46058</v>
       </c>
       <c r="E28" s="3">
-        <v>45973</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>90</v>
-      </c>
+        <v>46058</v>
+      </c>
+      <c r="F28" s="2"/>
       <c r="G28" s="4">
-        <v>-4257</v>
+        <v>-400.5</v>
       </c>
       <c r="H28" s="4">
-        <v>-893.97</v>
+        <v>-84.11</v>
       </c>
       <c r="I28" s="4">
-        <v>-5150.97</v>
+        <v>-484.61</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D29" s="3">
-        <v>45966</v>
+        <v>46058</v>
       </c>
       <c r="E29" s="3">
-        <v>45973</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>93</v>
-      </c>
+        <v>46058</v>
+      </c>
+      <c r="F29" s="2"/>
       <c r="G29" s="4">
-        <v>-3506</v>
+        <v>-405</v>
       </c>
       <c r="H29" s="4">
-        <v>-736.26</v>
+        <v>-85.05</v>
       </c>
       <c r="I29" s="4">
-        <v>-4242.26</v>
+        <v>-490.05</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D30" s="3">
-        <v>45959</v>
+        <v>46057</v>
       </c>
       <c r="E30" s="3">
-        <v>45966</v>
+        <v>46064</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="G30" s="4">
-        <v>-3201</v>
+        <v>-6236</v>
       </c>
       <c r="H30" s="4">
-        <v>-672.21</v>
+        <v>-1309.56</v>
       </c>
       <c r="I30" s="4">
-        <v>-3873.21</v>
+        <v>-7545.56</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="D31" s="3">
-        <v>45959</v>
+        <v>46057</v>
       </c>
       <c r="E31" s="3">
-        <v>45966</v>
+        <v>46064</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="G31" s="4">
-        <v>-2730</v>
+        <v>-5652</v>
       </c>
       <c r="H31" s="4">
-        <v>-573.3</v>
+        <v>-1186.92</v>
       </c>
       <c r="I31" s="4">
-        <v>-3303.3</v>
+        <v>-6838.92</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>11</v>
+        <v>95</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D32" s="3">
-        <v>45952</v>
+        <v>46057</v>
       </c>
       <c r="E32" s="3">
-        <v>45959</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>102</v>
-      </c>
+        <v>46057</v>
+      </c>
+      <c r="F32" s="2"/>
       <c r="G32" s="4">
-        <v>-3504</v>
+        <v>-200</v>
       </c>
       <c r="H32" s="4">
-        <v>-735.84</v>
+        <v>-42</v>
       </c>
       <c r="I32" s="4">
-        <v>-4239.84</v>
+        <v>-242</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D33" s="3">
-        <v>45952</v>
+        <v>46057</v>
       </c>
       <c r="E33" s="3">
-        <v>45959</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>105</v>
-      </c>
+        <v>46057</v>
+      </c>
+      <c r="F33" s="2"/>
       <c r="G33" s="4">
-        <v>-3098</v>
+        <v>-393</v>
       </c>
       <c r="H33" s="4">
-        <v>-650.58</v>
+        <v>-82.53</v>
       </c>
       <c r="I33" s="4">
-        <v>-3748.58</v>
+        <v>-475.53</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D34" s="3">
-        <v>45947</v>
+        <v>46056</v>
       </c>
       <c r="E34" s="3">
-        <v>45954</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>108</v>
-      </c>
+        <v>46056</v>
+      </c>
+      <c r="F34" s="2"/>
       <c r="G34" s="4">
-        <v>-1119</v>
+        <v>-100</v>
       </c>
       <c r="H34" s="4">
-        <v>-234.99</v>
+        <v>-21</v>
       </c>
       <c r="I34" s="4">
-        <v>-1353.99</v>
+        <v>-121</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D35" s="3">
+        <v>46053</v>
+      </c>
+      <c r="E35" s="3">
+        <v>46053</v>
+      </c>
+      <c r="F35" s="2"/>
+      <c r="G35" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="H35" s="4">
+        <v>-20</v>
+      </c>
+      <c r="I35" s="4">
+        <v>-1020</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D36" s="3">
+        <v>46052</v>
+      </c>
+      <c r="E36" s="3">
+        <v>46052</v>
+      </c>
+      <c r="F36" s="2"/>
+      <c r="G36" s="4">
+        <v>-402</v>
+      </c>
+      <c r="H36" s="4">
+        <v>-84.42</v>
+      </c>
+      <c r="I36" s="4">
+        <v>-486.42</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" s="2" t="s">
+      <c r="D37" s="3">
+        <v>46052</v>
+      </c>
+      <c r="E37" s="3">
+        <v>46052</v>
+      </c>
+      <c r="F37" s="2"/>
+      <c r="G37" s="4">
+        <v>-396</v>
+      </c>
+      <c r="H37" s="4">
+        <v>-83.16</v>
+      </c>
+      <c r="I37" s="4">
+        <v>-479.16</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D35" s="3">
+      <c r="B38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D38" s="3">
+        <v>46051</v>
+      </c>
+      <c r="E38" s="3">
+        <v>46058</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G38" s="4">
+        <v>-70</v>
+      </c>
+      <c r="H38" s="4">
+        <v>-14.7</v>
+      </c>
+      <c r="I38" s="4">
+        <v>-84.7</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D39" s="3">
+        <v>46050</v>
+      </c>
+      <c r="E39" s="3">
+        <v>46057</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G39" s="4">
+        <v>-3690</v>
+      </c>
+      <c r="H39" s="4">
+        <v>-774.9</v>
+      </c>
+      <c r="I39" s="4">
+        <v>-4464.9</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D40" s="3">
+        <v>46050</v>
+      </c>
+      <c r="E40" s="3">
+        <v>46057</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G40" s="4">
+        <v>-3338</v>
+      </c>
+      <c r="H40" s="4">
+        <v>-700.98</v>
+      </c>
+      <c r="I40" s="4">
+        <v>-4038.98</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D41" s="3">
+        <v>46050</v>
+      </c>
+      <c r="E41" s="3">
+        <v>46050</v>
+      </c>
+      <c r="F41" s="2"/>
+      <c r="G41" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H41" s="4">
+        <v>-0.21</v>
+      </c>
+      <c r="I41" s="4">
+        <v>-1.21</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D42" s="3">
+        <v>46045</v>
+      </c>
+      <c r="E42" s="3">
+        <v>46045</v>
+      </c>
+      <c r="F42" s="2"/>
+      <c r="G42" s="4">
+        <v>-396</v>
+      </c>
+      <c r="H42" s="4">
+        <v>-83.16</v>
+      </c>
+      <c r="I42" s="4">
+        <v>-479.16</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D43" s="3">
+        <v>46044</v>
+      </c>
+      <c r="E43" s="3">
+        <v>46051</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G43" s="4">
+        <v>-134</v>
+      </c>
+      <c r="H43" s="4">
+        <v>-28.14</v>
+      </c>
+      <c r="I43" s="4">
+        <v>-162.14</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D44" s="3">
+        <v>46044</v>
+      </c>
+      <c r="E44" s="3">
+        <v>46051</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="G44" s="4">
+        <v>-130</v>
+      </c>
+      <c r="H44" s="4">
+        <v>-27.3</v>
+      </c>
+      <c r="I44" s="4">
+        <v>-157.3</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D45" s="3">
+        <v>46043</v>
+      </c>
+      <c r="E45" s="3">
+        <v>46043</v>
+      </c>
+      <c r="F45" s="2"/>
+      <c r="G45" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H45" s="4">
+        <v>-0.21</v>
+      </c>
+      <c r="I45" s="4">
+        <v>-1.21</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D46" s="3">
+        <v>46043</v>
+      </c>
+      <c r="E46" s="3">
+        <v>46043</v>
+      </c>
+      <c r="F46" s="2"/>
+      <c r="G46" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H46" s="4">
+        <v>-0.21</v>
+      </c>
+      <c r="I46" s="4">
+        <v>-1.21</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D47" s="3">
+        <v>46043</v>
+      </c>
+      <c r="E47" s="3">
+        <v>46050</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G47" s="4">
+        <v>-3756</v>
+      </c>
+      <c r="H47" s="4">
+        <v>-788.76</v>
+      </c>
+      <c r="I47" s="4">
+        <v>-4544.76</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D48" s="3">
+        <v>46043</v>
+      </c>
+      <c r="E48" s="3">
+        <v>46050</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G48" s="4">
+        <v>-2816</v>
+      </c>
+      <c r="H48" s="4">
+        <v>-591.36</v>
+      </c>
+      <c r="I48" s="4">
+        <v>-3407.36</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D49" s="3">
+        <v>46038</v>
+      </c>
+      <c r="E49" s="3">
+        <v>46038</v>
+      </c>
+      <c r="F49" s="2"/>
+      <c r="G49" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H49" s="4">
+        <v>-0.21</v>
+      </c>
+      <c r="I49" s="4">
+        <v>-1.21</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D50" s="3">
+        <v>46036</v>
+      </c>
+      <c r="E50" s="3">
+        <v>46043</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G50" s="4">
+        <v>-3098</v>
+      </c>
+      <c r="H50" s="4">
+        <v>-650.58</v>
+      </c>
+      <c r="I50" s="4">
+        <v>-3748.58</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D51" s="3">
+        <v>46036</v>
+      </c>
+      <c r="E51" s="3">
+        <v>46043</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G51" s="4">
+        <v>-3218</v>
+      </c>
+      <c r="H51" s="4">
+        <v>-675.78</v>
+      </c>
+      <c r="I51" s="4">
+        <v>-3893.78</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D52" s="3">
+        <v>46030</v>
+      </c>
+      <c r="E52" s="3">
+        <v>46037</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G52" s="4">
+        <v>-3674</v>
+      </c>
+      <c r="H52" s="4">
+        <v>-771.54</v>
+      </c>
+      <c r="I52" s="4">
+        <v>-4445.54</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D53" s="3">
+        <v>46030</v>
+      </c>
+      <c r="E53" s="3">
+        <v>46037</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G53" s="4">
+        <v>-3066</v>
+      </c>
+      <c r="H53" s="4">
+        <v>-643.86</v>
+      </c>
+      <c r="I53" s="4">
+        <v>-3709.86</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D54" s="3">
+        <v>46026</v>
+      </c>
+      <c r="E54" s="3">
+        <v>46026</v>
+      </c>
+      <c r="F54" s="2"/>
+      <c r="G54" s="4">
+        <v>-200</v>
+      </c>
+      <c r="H54" s="4">
+        <v>-42</v>
+      </c>
+      <c r="I54" s="4">
+        <v>-242</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D55" s="3">
+        <v>46025</v>
+      </c>
+      <c r="E55" s="3">
+        <v>46025</v>
+      </c>
+      <c r="F55" s="2"/>
+      <c r="G55" s="4">
+        <v>-100</v>
+      </c>
+      <c r="H55" s="4">
+        <v>-21</v>
+      </c>
+      <c r="I55" s="4">
+        <v>-121</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D56" s="3">
+        <v>46022</v>
+      </c>
+      <c r="E56" s="3">
+        <v>46022</v>
+      </c>
+      <c r="F56" s="2"/>
+      <c r="G56" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="H56" s="4">
+        <v>-20</v>
+      </c>
+      <c r="I56" s="4">
+        <v>-1020</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D57" s="3">
+        <v>46020</v>
+      </c>
+      <c r="E57" s="3">
+        <v>46027</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="G57" s="4">
+        <v>-134</v>
+      </c>
+      <c r="H57" s="4">
+        <v>-28.14</v>
+      </c>
+      <c r="I57" s="4">
+        <v>-162.14</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D58" s="3">
+        <v>46020</v>
+      </c>
+      <c r="E58" s="3">
+        <v>46027</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="G58" s="4">
+        <v>-130</v>
+      </c>
+      <c r="H58" s="4">
+        <v>-27.3</v>
+      </c>
+      <c r="I58" s="4">
+        <v>-157.3</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D59" s="3">
+        <v>46016</v>
+      </c>
+      <c r="E59" s="3">
+        <v>46016</v>
+      </c>
+      <c r="F59" s="2"/>
+      <c r="G59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H59" s="4">
+        <v>-0.21</v>
+      </c>
+      <c r="I59" s="4">
+        <v>-1.21</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D60" s="3">
+        <v>46016</v>
+      </c>
+      <c r="E60" s="3">
+        <v>46016</v>
+      </c>
+      <c r="F60" s="2"/>
+      <c r="G60" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H60" s="4">
+        <v>-0.21</v>
+      </c>
+      <c r="I60" s="4">
+        <v>-1.21</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D61" s="3">
+        <v>46009</v>
+      </c>
+      <c r="E61" s="3">
+        <v>46009</v>
+      </c>
+      <c r="F61" s="2"/>
+      <c r="G61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H61" s="4">
+        <v>-0.21</v>
+      </c>
+      <c r="I61" s="4">
+        <v>-1.21</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D62" s="3">
+        <v>46009</v>
+      </c>
+      <c r="E62" s="3">
+        <v>46009</v>
+      </c>
+      <c r="F62" s="2"/>
+      <c r="G62" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H62" s="4">
+        <v>-0.21</v>
+      </c>
+      <c r="I62" s="4">
+        <v>-1.21</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D63" s="3">
+        <v>46008</v>
+      </c>
+      <c r="E63" s="3">
+        <v>46015</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G63" s="4">
+        <v>-3560</v>
+      </c>
+      <c r="H63" s="4">
+        <v>-747.6</v>
+      </c>
+      <c r="I63" s="4">
+        <v>-4307.6</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D64" s="3">
+        <v>46008</v>
+      </c>
+      <c r="E64" s="3">
+        <v>46015</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G64" s="4">
+        <v>-3246</v>
+      </c>
+      <c r="H64" s="4">
+        <v>-681.66</v>
+      </c>
+      <c r="I64" s="4">
+        <v>-3927.66</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D65" s="3">
+        <v>46002</v>
+      </c>
+      <c r="E65" s="3">
+        <v>46002</v>
+      </c>
+      <c r="F65" s="2"/>
+      <c r="G65" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H65" s="4">
+        <v>-0.21</v>
+      </c>
+      <c r="I65" s="4">
+        <v>-1.21</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D66" s="3">
+        <v>46001</v>
+      </c>
+      <c r="E66" s="3">
+        <v>46008</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="G66" s="4">
+        <v>-3124</v>
+      </c>
+      <c r="H66" s="4">
+        <v>-656.04</v>
+      </c>
+      <c r="I66" s="4">
+        <v>-3780.04</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D67" s="3">
+        <v>46001</v>
+      </c>
+      <c r="E67" s="3">
+        <v>46008</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="G67" s="4">
+        <v>-3648</v>
+      </c>
+      <c r="H67" s="4">
+        <v>-766.08</v>
+      </c>
+      <c r="I67" s="4">
+        <v>-4414.08</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D68" s="3">
+        <v>46001</v>
+      </c>
+      <c r="E68" s="3">
+        <v>46008</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="G68" s="4">
+        <v>-3124</v>
+      </c>
+      <c r="H68" s="4">
+        <v>-656.04</v>
+      </c>
+      <c r="I68" s="4">
+        <v>-3780.04</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D69" s="3">
+        <v>45987</v>
+      </c>
+      <c r="E69" s="3">
+        <v>45987</v>
+      </c>
+      <c r="F69" s="2"/>
+      <c r="G69" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H69" s="4">
+        <v>-0.21</v>
+      </c>
+      <c r="I69" s="4">
+        <v>-1.21</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D70" s="3">
+        <v>45996</v>
+      </c>
+      <c r="E70" s="3">
+        <v>45996</v>
+      </c>
+      <c r="F70" s="2"/>
+      <c r="G70" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H70" s="4">
+        <v>-0.21</v>
+      </c>
+      <c r="I70" s="4">
+        <v>-1.21</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D71" s="3">
+        <v>45996</v>
+      </c>
+      <c r="E71" s="3">
+        <v>45996</v>
+      </c>
+      <c r="F71" s="2"/>
+      <c r="G71" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H71" s="4">
+        <v>-0.21</v>
+      </c>
+      <c r="I71" s="4">
+        <v>-1.21</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D72" s="3">
+        <v>45996</v>
+      </c>
+      <c r="E72" s="3">
+        <v>45996</v>
+      </c>
+      <c r="F72" s="2"/>
+      <c r="G72" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H72" s="4">
+        <v>-0.21</v>
+      </c>
+      <c r="I72" s="4">
+        <v>-1.21</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D73" s="3">
+        <v>45996</v>
+      </c>
+      <c r="E73" s="3">
+        <v>45996</v>
+      </c>
+      <c r="F73" s="2"/>
+      <c r="G73" s="4">
+        <v>-200</v>
+      </c>
+      <c r="H73" s="4">
+        <v>-42</v>
+      </c>
+      <c r="I73" s="4">
+        <v>-242</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D74" s="3">
+        <v>45995</v>
+      </c>
+      <c r="E74" s="3">
+        <v>45995</v>
+      </c>
+      <c r="F74" s="2"/>
+      <c r="G74" s="4">
+        <v>-100</v>
+      </c>
+      <c r="H74" s="4">
+        <v>-21</v>
+      </c>
+      <c r="I74" s="4">
+        <v>-121</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
+      <c r="A75" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D75" s="3">
+        <v>45994</v>
+      </c>
+      <c r="E75" s="3">
+        <v>46001</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="G75" s="4">
+        <v>-2980</v>
+      </c>
+      <c r="H75" s="4">
+        <v>-625.8</v>
+      </c>
+      <c r="I75" s="4">
+        <v>-3605.8</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="A76" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D76" s="3">
+        <v>45994</v>
+      </c>
+      <c r="E76" s="3">
+        <v>46001</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="G76" s="4">
+        <v>-3436</v>
+      </c>
+      <c r="H76" s="4">
+        <v>-721.5599999999999</v>
+      </c>
+      <c r="I76" s="4">
+        <v>-4157.56</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10">
+      <c r="A77" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D77" s="3">
+        <v>45991</v>
+      </c>
+      <c r="E77" s="3">
+        <v>45991</v>
+      </c>
+      <c r="F77" s="2"/>
+      <c r="G77" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="H77" s="4">
+        <v>-20</v>
+      </c>
+      <c r="I77" s="4">
+        <v>-1020</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10">
+      <c r="A78" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D78" s="3">
+        <v>45987</v>
+      </c>
+      <c r="E78" s="3">
+        <v>45987</v>
+      </c>
+      <c r="F78" s="2"/>
+      <c r="G78" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H78" s="4">
+        <v>-0.21</v>
+      </c>
+      <c r="I78" s="4">
+        <v>-1.21</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
+      <c r="A79" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D79" s="3">
+        <v>45987</v>
+      </c>
+      <c r="E79" s="3">
+        <v>45987</v>
+      </c>
+      <c r="F79" s="2"/>
+      <c r="G79" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H79" s="4">
+        <v>-0.21</v>
+      </c>
+      <c r="I79" s="4">
+        <v>-1.21</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
+      <c r="A80" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D80" s="3">
+        <v>45987</v>
+      </c>
+      <c r="E80" s="3">
+        <v>45994</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="G80" s="4">
+        <v>-3262</v>
+      </c>
+      <c r="H80" s="4">
+        <v>-685.02</v>
+      </c>
+      <c r="I80" s="4">
+        <v>-3947.02</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
+      <c r="A81" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D81" s="3">
+        <v>45987</v>
+      </c>
+      <c r="E81" s="3">
+        <v>45994</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G81" s="4">
+        <v>-3054</v>
+      </c>
+      <c r="H81" s="4">
+        <v>-641.34</v>
+      </c>
+      <c r="I81" s="4">
+        <v>-3695.34</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
+      <c r="A82" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D82" s="3">
+        <v>45980</v>
+      </c>
+      <c r="E82" s="3">
+        <v>45987</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="G82" s="4">
+        <v>-2908</v>
+      </c>
+      <c r="H82" s="4">
+        <v>-610.6799999999999</v>
+      </c>
+      <c r="I82" s="4">
+        <v>-3518.68</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
+      <c r="A83" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D83" s="3">
+        <v>45980</v>
+      </c>
+      <c r="E83" s="3">
+        <v>45987</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="G83" s="4">
+        <v>-2954</v>
+      </c>
+      <c r="H83" s="4">
+        <v>-620.34</v>
+      </c>
+      <c r="I83" s="4">
+        <v>-3574.34</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10">
+      <c r="A84" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D84" s="3">
+        <v>45980</v>
+      </c>
+      <c r="E84" s="3">
+        <v>45980</v>
+      </c>
+      <c r="F84" s="2"/>
+      <c r="G84" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H84" s="4">
+        <v>-0.21</v>
+      </c>
+      <c r="I84" s="4">
+        <v>-1.21</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="A85" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D85" s="3">
+        <v>45980</v>
+      </c>
+      <c r="E85" s="3">
+        <v>45980</v>
+      </c>
+      <c r="F85" s="2"/>
+      <c r="G85" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H85" s="4">
+        <v>-0.21</v>
+      </c>
+      <c r="I85" s="4">
+        <v>-1.21</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="A86" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D86" s="3">
+        <v>45980</v>
+      </c>
+      <c r="E86" s="3">
+        <v>45980</v>
+      </c>
+      <c r="F86" s="2"/>
+      <c r="G86" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H86" s="4">
+        <v>-0.21</v>
+      </c>
+      <c r="I86" s="4">
+        <v>-1.21</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
+      <c r="A87" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D87" s="3">
+        <v>45973</v>
+      </c>
+      <c r="E87" s="3">
+        <v>45980</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="G87" s="4">
+        <v>-3704</v>
+      </c>
+      <c r="H87" s="4">
+        <v>-777.84</v>
+      </c>
+      <c r="I87" s="4">
+        <v>-4481.84</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10">
+      <c r="A88" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D88" s="3">
+        <v>45973</v>
+      </c>
+      <c r="E88" s="3">
+        <v>45980</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="G88" s="4">
+        <v>-3338</v>
+      </c>
+      <c r="H88" s="4">
+        <v>-700.98</v>
+      </c>
+      <c r="I88" s="4">
+        <v>-4038.98</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10">
+      <c r="A89" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D89" s="3">
+        <v>45973</v>
+      </c>
+      <c r="E89" s="3">
+        <v>45973</v>
+      </c>
+      <c r="F89" s="2"/>
+      <c r="G89" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H89" s="4">
+        <v>-0.21</v>
+      </c>
+      <c r="I89" s="4">
+        <v>-1.21</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10">
+      <c r="A90" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D90" s="3">
+        <v>45973</v>
+      </c>
+      <c r="E90" s="3">
+        <v>45973</v>
+      </c>
+      <c r="F90" s="2"/>
+      <c r="G90" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H90" s="4">
+        <v>-0.21</v>
+      </c>
+      <c r="I90" s="4">
+        <v>-1.21</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10">
+      <c r="A91" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D91" s="3">
+        <v>45973</v>
+      </c>
+      <c r="E91" s="3">
+        <v>45973</v>
+      </c>
+      <c r="F91" s="2"/>
+      <c r="G91" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H91" s="4">
+        <v>-0.21</v>
+      </c>
+      <c r="I91" s="4">
+        <v>-1.21</v>
+      </c>
+      <c r="J91" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10">
+      <c r="A92" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D92" s="3">
+        <v>45967</v>
+      </c>
+      <c r="E92" s="3">
+        <v>45967</v>
+      </c>
+      <c r="F92" s="2"/>
+      <c r="G92" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H92" s="4">
+        <v>-0.21</v>
+      </c>
+      <c r="I92" s="4">
+        <v>-1.21</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10">
+      <c r="A93" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D93" s="3">
+        <v>45967</v>
+      </c>
+      <c r="E93" s="3">
+        <v>45967</v>
+      </c>
+      <c r="F93" s="2"/>
+      <c r="G93" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H93" s="4">
+        <v>-0.21</v>
+      </c>
+      <c r="I93" s="4">
+        <v>-1.21</v>
+      </c>
+      <c r="J93" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10">
+      <c r="A94" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D94" s="3">
+        <v>45967</v>
+      </c>
+      <c r="E94" s="3">
+        <v>45967</v>
+      </c>
+      <c r="F94" s="2"/>
+      <c r="G94" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H94" s="4">
+        <v>-0.21</v>
+      </c>
+      <c r="I94" s="4">
+        <v>-1.21</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10">
+      <c r="A95" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D95" s="3">
+        <v>45967</v>
+      </c>
+      <c r="E95" s="3">
+        <v>45967</v>
+      </c>
+      <c r="F95" s="2"/>
+      <c r="G95" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H95" s="4">
+        <v>-0.21</v>
+      </c>
+      <c r="I95" s="4">
+        <v>-1.21</v>
+      </c>
+      <c r="J95" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10">
+      <c r="A96" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D96" s="3">
+        <v>45967</v>
+      </c>
+      <c r="E96" s="3">
+        <v>45967</v>
+      </c>
+      <c r="F96" s="2"/>
+      <c r="G96" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H96" s="4">
+        <v>-0.21</v>
+      </c>
+      <c r="I96" s="4">
+        <v>-1.21</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10">
+      <c r="A97" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D97" s="3">
+        <v>45967</v>
+      </c>
+      <c r="E97" s="3">
+        <v>45967</v>
+      </c>
+      <c r="F97" s="2"/>
+      <c r="G97" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H97" s="4">
+        <v>-0.21</v>
+      </c>
+      <c r="I97" s="4">
+        <v>-1.21</v>
+      </c>
+      <c r="J97" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10">
+      <c r="A98" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D98" s="3">
+        <v>45966</v>
+      </c>
+      <c r="E98" s="3">
+        <v>45973</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="G98" s="4">
+        <v>-3692</v>
+      </c>
+      <c r="H98" s="4">
+        <v>-775.3200000000001</v>
+      </c>
+      <c r="I98" s="4">
+        <v>-4467.32</v>
+      </c>
+      <c r="J98" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10">
+      <c r="A99" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D99" s="3">
+        <v>45966</v>
+      </c>
+      <c r="E99" s="3">
+        <v>45973</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="G99" s="4">
+        <v>-2912</v>
+      </c>
+      <c r="H99" s="4">
+        <v>-611.52</v>
+      </c>
+      <c r="I99" s="4">
+        <v>-3523.52</v>
+      </c>
+      <c r="J99" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10">
+      <c r="A100" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D100" s="3">
+        <v>45965</v>
+      </c>
+      <c r="E100" s="3">
+        <v>45965</v>
+      </c>
+      <c r="F100" s="2"/>
+      <c r="G100" s="4">
+        <v>-200</v>
+      </c>
+      <c r="H100" s="4">
+        <v>-42</v>
+      </c>
+      <c r="I100" s="4">
+        <v>-242</v>
+      </c>
+      <c r="J100" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10">
+      <c r="A101" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D101" s="3">
+        <v>45964</v>
+      </c>
+      <c r="E101" s="3">
+        <v>45964</v>
+      </c>
+      <c r="F101" s="2"/>
+      <c r="G101" s="4">
+        <v>-100</v>
+      </c>
+      <c r="H101" s="4">
+        <v>-21</v>
+      </c>
+      <c r="I101" s="4">
+        <v>-121</v>
+      </c>
+      <c r="J101" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10">
+      <c r="A102" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D102" s="3">
+        <v>45961</v>
+      </c>
+      <c r="E102" s="3">
+        <v>45961</v>
+      </c>
+      <c r="F102" s="2"/>
+      <c r="G102" s="4">
+        <v>-1000</v>
+      </c>
+      <c r="H102" s="4">
+        <v>-20</v>
+      </c>
+      <c r="I102" s="4">
+        <v>-1020</v>
+      </c>
+      <c r="J102" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10">
+      <c r="A103" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D103" s="3">
+        <v>45959</v>
+      </c>
+      <c r="E103" s="3">
+        <v>45966</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="G103" s="4">
+        <v>-3124</v>
+      </c>
+      <c r="H103" s="4">
+        <v>-656.04</v>
+      </c>
+      <c r="I103" s="4">
+        <v>-3780.04</v>
+      </c>
+      <c r="J103" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10">
+      <c r="A104" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D104" s="3">
+        <v>45959</v>
+      </c>
+      <c r="E104" s="3">
+        <v>45966</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="G104" s="4">
+        <v>-3410</v>
+      </c>
+      <c r="H104" s="4">
+        <v>-716.1</v>
+      </c>
+      <c r="I104" s="4">
+        <v>-4126.1</v>
+      </c>
+      <c r="J104" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10">
+      <c r="A105" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D105" s="3">
+        <v>45952</v>
+      </c>
+      <c r="E105" s="3">
+        <v>45959</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="G105" s="4">
+        <v>-3070</v>
+      </c>
+      <c r="H105" s="4">
+        <v>-644.7</v>
+      </c>
+      <c r="I105" s="4">
+        <v>-3714.7</v>
+      </c>
+      <c r="J105" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10">
+      <c r="A106" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D106" s="3">
+        <v>45952</v>
+      </c>
+      <c r="E106" s="3">
+        <v>45959</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="G106" s="4">
+        <v>-3570</v>
+      </c>
+      <c r="H106" s="4">
+        <v>-749.7</v>
+      </c>
+      <c r="I106" s="4">
+        <v>-4319.7</v>
+      </c>
+      <c r="J106" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10">
+      <c r="A107" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D107" s="3">
+        <v>45954</v>
+      </c>
+      <c r="E107" s="3">
+        <v>45954</v>
+      </c>
+      <c r="F107" s="2"/>
+      <c r="G107" s="4">
+        <v>-1</v>
+      </c>
+      <c r="H107" s="4">
+        <v>-0.21</v>
+      </c>
+      <c r="I107" s="4">
+        <v>-1.21</v>
+      </c>
+      <c r="J107" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10">
+      <c r="A108" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D108" s="3">
         <v>45947</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E108" s="3">
         <v>45954</v>
       </c>
-      <c r="F35" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="G35" s="4">
-        <v>-882</v>
-      </c>
-      <c r="H35" s="4">
-        <v>-185.22</v>
-      </c>
-      <c r="I35" s="4">
-        <v>-1067.22</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>14</v>
+      <c r="F108" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="G108" s="4">
+        <v>-934</v>
+      </c>
+      <c r="H108" s="4">
+        <v>-196.14</v>
+      </c>
+      <c r="I108" s="4">
+        <v>-1130.14</v>
+      </c>
+      <c r="J108" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10">
+      <c r="A109" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D109" s="3">
+        <v>45947</v>
+      </c>
+      <c r="E109" s="3">
+        <v>45954</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="G109" s="4">
+        <v>-1086</v>
+      </c>
+      <c r="H109" s="4">
+        <v>-228.06</v>
+      </c>
+      <c r="I109" s="4">
+        <v>-1314.06</v>
+      </c>
+      <c r="J109" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10">
+      <c r="A110" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D110" s="3">
+        <v>45935</v>
+      </c>
+      <c r="E110" s="3">
+        <v>45935</v>
+      </c>
+      <c r="F110" s="2"/>
+      <c r="G110" s="4">
+        <v>-46.67</v>
+      </c>
+      <c r="H110" s="4">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="I110" s="4">
+        <v>-56.47</v>
+      </c>
+      <c r="J110" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10">
+      <c r="A111" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D111" s="3">
+        <v>45934</v>
+      </c>
+      <c r="E111" s="3">
+        <v>45934</v>
+      </c>
+      <c r="F111" s="2"/>
+      <c r="G111" s="4">
+        <v>-20</v>
+      </c>
+      <c r="H111" s="4">
+        <v>-4.2</v>
+      </c>
+      <c r="I111" s="4">
+        <v>-24.2</v>
+      </c>
+      <c r="J111" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10">
+      <c r="A112" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D112" s="3">
+        <v>45931</v>
+      </c>
+      <c r="E112" s="3">
+        <v>45931</v>
+      </c>
+      <c r="F112" s="2"/>
+      <c r="G112" s="4">
+        <v>-100</v>
+      </c>
+      <c r="H112" s="4">
+        <v>-2</v>
+      </c>
+      <c r="I112" s="4">
+        <v>-102</v>
+      </c>
+      <c r="J112" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
